--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/31.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/31.xlsx
@@ -426,13 +426,13 @@
         <v>-7.321259196304797</v>
       </c>
       <c r="E2">
-        <v>-14.99145640893822</v>
+        <v>-18.95405230461009</v>
       </c>
       <c r="F2">
-        <v>-3.265054168854108</v>
+        <v>-3.904918285472557</v>
       </c>
       <c r="G2">
-        <v>-15.15754081131767</v>
+        <v>-15.06445489184444</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.384756135255421</v>
       </c>
       <c r="E3">
-        <v>-15.83953996414671</v>
+        <v>-19.23635284577425</v>
       </c>
       <c r="F3">
-        <v>-3.088780899007984</v>
+        <v>-3.807448435022154</v>
       </c>
       <c r="G3">
-        <v>-13.45218776403675</v>
+        <v>-15.22057359838539</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.488767918031423</v>
       </c>
       <c r="E4">
-        <v>-14.21253170877487</v>
+        <v>-19.33653627624594</v>
       </c>
       <c r="F4">
-        <v>-3.043177616749066</v>
+        <v>-3.444417249112673</v>
       </c>
       <c r="G4">
-        <v>-14.11479345372188</v>
+        <v>-14.9589461502351</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.616643506956764</v>
       </c>
       <c r="E5">
-        <v>-15.59444989390357</v>
+        <v>-20.28126652372613</v>
       </c>
       <c r="F5">
-        <v>-2.884582535646086</v>
+        <v>-3.320955714664629</v>
       </c>
       <c r="G5">
-        <v>-14.09523475067586</v>
+        <v>-14.88145786607015</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.752039502444227</v>
       </c>
       <c r="E6">
-        <v>-17.07224040224867</v>
+        <v>-20.23364961953548</v>
       </c>
       <c r="F6">
-        <v>-3.057220100961323</v>
+        <v>-3.417349515858797</v>
       </c>
       <c r="G6">
-        <v>-14.45020965139699</v>
+        <v>-14.73098198440088</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.882796621195275</v>
       </c>
       <c r="E7">
-        <v>-16.57835144155011</v>
+        <v>-20.35265791645706</v>
       </c>
       <c r="F7">
-        <v>-2.735554269678038</v>
+        <v>-3.538947223650541</v>
       </c>
       <c r="G7">
-        <v>-14.14105601148492</v>
+        <v>-14.33458719316517</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.998047978635918</v>
       </c>
       <c r="E8">
-        <v>-16.47702683562849</v>
+        <v>-22.13775067096266</v>
       </c>
       <c r="F8">
-        <v>-3.084784026289476</v>
+        <v>-3.528106379450104</v>
       </c>
       <c r="G8">
-        <v>-14.55329176312604</v>
+        <v>-14.43107966399831</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.076203420773263</v>
       </c>
       <c r="E9">
-        <v>-16.99047427556617</v>
+        <v>-22.21492492500138</v>
       </c>
       <c r="F9">
-        <v>-2.294664003212029</v>
+        <v>-3.424805650851395</v>
       </c>
       <c r="G9">
-        <v>-12.97120522372712</v>
+        <v>-13.92978361625971</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.105623220051918</v>
       </c>
       <c r="E10">
-        <v>-18.72761501880455</v>
+        <v>-21.90027749400042</v>
       </c>
       <c r="F10">
-        <v>-2.420241188006823</v>
+        <v>-2.975857026290953</v>
       </c>
       <c r="G10">
-        <v>-12.62604443525716</v>
+        <v>-14.33569953646637</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.081030035482991</v>
       </c>
       <c r="E11">
-        <v>-18.70129099939796</v>
+        <v>-23.04488099875716</v>
       </c>
       <c r="F11">
-        <v>-2.80555545705161</v>
+        <v>-3.039668652430807</v>
       </c>
       <c r="G11">
-        <v>-11.85804752832934</v>
+        <v>-13.60730668582484</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.99024522302902</v>
       </c>
       <c r="E12">
-        <v>-18.00428186555936</v>
+        <v>-24.30434018977044</v>
       </c>
       <c r="F12">
-        <v>-2.196244843718017</v>
+        <v>-2.901166451050132</v>
       </c>
       <c r="G12">
-        <v>-11.95918469455407</v>
+        <v>-13.35964477403196</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.829842166007466</v>
       </c>
       <c r="E13">
-        <v>-19.38716914412571</v>
+        <v>-23.93769229173941</v>
       </c>
       <c r="F13">
-        <v>-1.751246703301526</v>
+        <v>-2.737143078356608</v>
       </c>
       <c r="G13">
-        <v>-12.5665737951897</v>
+        <v>-12.71464125497914</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.609726135806381</v>
       </c>
       <c r="E14">
-        <v>-19.30825142759403</v>
+        <v>-24.91755444057111</v>
       </c>
       <c r="F14">
-        <v>-1.993168918186913</v>
+        <v>-2.958991465969955</v>
       </c>
       <c r="G14">
-        <v>-12.19947402143099</v>
+        <v>-12.45211830426047</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.333076954672846</v>
       </c>
       <c r="E15">
-        <v>-21.0443234509666</v>
+        <v>-25.46211702541549</v>
       </c>
       <c r="F15">
-        <v>-1.090395070165747</v>
+        <v>-2.225355330987198</v>
       </c>
       <c r="G15">
-        <v>-11.5647662990053</v>
+        <v>-11.98228899187265</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.010815774788628</v>
       </c>
       <c r="E16">
-        <v>-22.00005789028543</v>
+        <v>-25.74599347553432</v>
       </c>
       <c r="F16">
-        <v>-1.50301647064382</v>
+        <v>-2.505163757407023</v>
       </c>
       <c r="G16">
-        <v>-11.59439568158178</v>
+        <v>-11.93135293820542</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.667362517992401</v>
       </c>
       <c r="E17">
-        <v>-22.77959393443982</v>
+        <v>-26.52633105958806</v>
       </c>
       <c r="F17">
-        <v>-0.8923498198718444</v>
+        <v>-2.189202064059416</v>
       </c>
       <c r="G17">
-        <v>-11.60375128327576</v>
+        <v>-11.37404245994235</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.319940469190826</v>
       </c>
       <c r="E18">
-        <v>-22.80431487404769</v>
+        <v>-26.39195765035846</v>
       </c>
       <c r="F18">
-        <v>-0.9174617776877114</v>
+        <v>-1.862793001027702</v>
       </c>
       <c r="G18">
-        <v>-10.95031580473441</v>
+        <v>-11.39548486340021</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.982647656157824</v>
       </c>
       <c r="E19">
-        <v>-25.0812089627343</v>
+        <v>-28.500546474076</v>
       </c>
       <c r="F19">
-        <v>-0.9050039603170096</v>
+        <v>-1.710203583595019</v>
       </c>
       <c r="G19">
-        <v>-10.22494548217024</v>
+        <v>-10.66250028609572</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.673671757474898</v>
       </c>
       <c r="E20">
-        <v>-24.81401541085973</v>
+        <v>-28.66105370680387</v>
       </c>
       <c r="F20">
-        <v>-0.3395959909643875</v>
+        <v>-1.74439196304336</v>
       </c>
       <c r="G20">
-        <v>-10.23509230424811</v>
+        <v>-10.95341447535917</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.398868320529441</v>
       </c>
       <c r="E21">
-        <v>-25.58580323598699</v>
+        <v>-29.02022509424824</v>
       </c>
       <c r="F21">
-        <v>-0.3240947517558003</v>
+        <v>-1.283132970509914</v>
       </c>
       <c r="G21">
-        <v>-8.987370864315574</v>
+        <v>-10.47860279193474</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.15478179957474</v>
       </c>
       <c r="E22">
-        <v>-25.1338660584955</v>
+        <v>-29.7405943612554</v>
       </c>
       <c r="F22">
-        <v>-0.3673578961018101</v>
+        <v>-1.502113550174769</v>
       </c>
       <c r="G22">
-        <v>-10.43226508602156</v>
+        <v>-10.54848840826876</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.942015740715548</v>
       </c>
       <c r="E23">
-        <v>-27.04303900081127</v>
+        <v>-30.53474605526954</v>
       </c>
       <c r="F23">
-        <v>-0.1668234017624946</v>
+        <v>-1.002232755853199</v>
       </c>
       <c r="G23">
-        <v>-9.339788368607611</v>
+        <v>-10.53697764142871</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.755710752791565</v>
       </c>
       <c r="E24">
-        <v>-26.18691287576516</v>
+        <v>-30.46884317303591</v>
       </c>
       <c r="F24">
-        <v>0.6769905679970134</v>
+        <v>-1.097088278780367</v>
       </c>
       <c r="G24">
-        <v>-8.738633025222434</v>
+        <v>-10.11342644513435</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.584289916537645</v>
       </c>
       <c r="E25">
-        <v>-27.59131493434194</v>
+        <v>-30.60724239565834</v>
       </c>
       <c r="F25">
-        <v>0.2500268143068698</v>
+        <v>-0.9947873896368369</v>
       </c>
       <c r="G25">
-        <v>-8.715227468259787</v>
+        <v>-10.30103837139039</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.422545194428</v>
       </c>
       <c r="E26">
-        <v>-27.10660519045694</v>
+        <v>-31.22597685627435</v>
       </c>
       <c r="F26">
-        <v>0.4046979190227879</v>
+        <v>-1.171502179308653</v>
       </c>
       <c r="G26">
-        <v>-8.874027716687547</v>
+        <v>-10.42164816647712</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.266655523126364</v>
       </c>
       <c r="E27">
-        <v>-27.18479835114738</v>
+        <v>-31.27268580142647</v>
       </c>
       <c r="F27">
-        <v>0.376796848161695</v>
+        <v>-0.920053739291071</v>
       </c>
       <c r="G27">
-        <v>-8.425508385936007</v>
+        <v>-9.846712343762972</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.107561517025775</v>
       </c>
       <c r="E28">
-        <v>-27.42398329128451</v>
+        <v>-30.83842778646092</v>
       </c>
       <c r="F28">
-        <v>0.3531221077896851</v>
+        <v>-0.8797312992249995</v>
       </c>
       <c r="G28">
-        <v>-8.978634334637437</v>
+        <v>-10.3202759515191</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.942304267861429</v>
       </c>
       <c r="E29">
-        <v>-27.75885035872971</v>
+        <v>-31.04455033786805</v>
       </c>
       <c r="F29">
-        <v>0.5065398926251675</v>
+        <v>-0.9706777563783572</v>
       </c>
       <c r="G29">
-        <v>-9.399997260330336</v>
+        <v>-10.46483423303691</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.77364032625061</v>
       </c>
       <c r="E30">
-        <v>-27.41890234344791</v>
+        <v>-31.14787426506406</v>
       </c>
       <c r="F30">
-        <v>0.2607193807422059</v>
+        <v>-1.202869967750462</v>
       </c>
       <c r="G30">
-        <v>-8.444457948602796</v>
+        <v>-9.977319986378298</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.599364756446028</v>
       </c>
       <c r="E31">
-        <v>-27.63870541483221</v>
+        <v>-30.5096900085851</v>
       </c>
       <c r="F31">
-        <v>-0.4823576575302571</v>
+        <v>-0.7747332458179538</v>
       </c>
       <c r="G31">
-        <v>-8.520762712737458</v>
+        <v>-10.05228066902402</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.421915270690942</v>
       </c>
       <c r="E32">
-        <v>-26.25685968528763</v>
+        <v>-29.98027064082237</v>
       </c>
       <c r="F32">
-        <v>0.1364742107311136</v>
+        <v>-0.7859062653469135</v>
       </c>
       <c r="G32">
-        <v>-8.663546541846223</v>
+        <v>-9.676907841962674</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.251429012525808</v>
       </c>
       <c r="E33">
-        <v>-27.34452215787192</v>
+        <v>-30.37204704112196</v>
       </c>
       <c r="F33">
-        <v>0.01761260047081534</v>
+        <v>-1.118946409438038</v>
       </c>
       <c r="G33">
-        <v>-8.218486731183223</v>
+        <v>-10.28981562201226</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.09128487565426</v>
       </c>
       <c r="E34">
-        <v>-25.32050711472163</v>
+        <v>-29.79729312006844</v>
       </c>
       <c r="F34">
-        <v>0.263110877434088</v>
+        <v>-1.161272670251482</v>
       </c>
       <c r="G34">
-        <v>-8.769732290018347</v>
+        <v>-10.36670635270738</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.94646724999763</v>
       </c>
       <c r="E35">
-        <v>-26.6176296240567</v>
+        <v>-29.73737914470995</v>
       </c>
       <c r="F35">
-        <v>0.0449876580311306</v>
+        <v>-1.204601255622312</v>
       </c>
       <c r="G35">
-        <v>-7.391416449652642</v>
+        <v>-10.15769837063103</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.826253725184583</v>
       </c>
       <c r="E36">
-        <v>-25.38988333651914</v>
+        <v>-29.06736650866808</v>
       </c>
       <c r="F36">
-        <v>0.1488458778919242</v>
+        <v>-1.08255457269825</v>
       </c>
       <c r="G36">
-        <v>-9.059418266886734</v>
+        <v>-10.37311225832586</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.732101649086586</v>
       </c>
       <c r="E37">
-        <v>-25.34533220923168</v>
+        <v>-27.93455062175331</v>
       </c>
       <c r="F37">
-        <v>0.3354314935354988</v>
+        <v>-1.294735912720927</v>
       </c>
       <c r="G37">
-        <v>-8.429616772950244</v>
+        <v>-10.41675849071562</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.664515894260875</v>
       </c>
       <c r="E38">
-        <v>-25.18916325460316</v>
+        <v>-28.31755083942604</v>
       </c>
       <c r="F38">
-        <v>-0.1431304373076231</v>
+        <v>-1.440020786395724</v>
       </c>
       <c r="G38">
-        <v>-8.494606092431676</v>
+        <v>-10.30227651542208</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.627218494297718</v>
       </c>
       <c r="E39">
-        <v>-24.10672664102372</v>
+        <v>-27.93420192925472</v>
       </c>
       <c r="F39">
-        <v>0.08362105696289394</v>
+        <v>-1.280130138674766</v>
       </c>
       <c r="G39">
-        <v>-7.658706585947859</v>
+        <v>-9.644189720398057</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.616966180352771</v>
       </c>
       <c r="E40">
-        <v>-22.59608205375298</v>
+        <v>-27.45723134744883</v>
       </c>
       <c r="F40">
-        <v>-0.1025081282417382</v>
+        <v>-1.179722069046632</v>
       </c>
       <c r="G40">
-        <v>-7.80791287340281</v>
+        <v>-9.820158457992477</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.627711636553243</v>
       </c>
       <c r="E41">
-        <v>-22.28695483256738</v>
+        <v>-26.47571630560433</v>
       </c>
       <c r="F41">
-        <v>-0.2101205091720192</v>
+        <v>-1.200268894105671</v>
       </c>
       <c r="G41">
-        <v>-7.910125966927809</v>
+        <v>-9.687723394239473</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.656565286120228</v>
       </c>
       <c r="E42">
-        <v>-22.61766928934755</v>
+        <v>-26.4427535433025</v>
       </c>
       <c r="F42">
-        <v>-0.2423406876713087</v>
+        <v>-1.146209637398975</v>
       </c>
       <c r="G42">
-        <v>-8.552653197917257</v>
+        <v>-10.49353666286239</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.696913054932581</v>
       </c>
       <c r="E43">
-        <v>-21.33183626571359</v>
+        <v>-25.84478666448566</v>
       </c>
       <c r="F43">
-        <v>-0.4387855321430031</v>
+        <v>-1.279662111092184</v>
       </c>
       <c r="G43">
-        <v>-8.792085093499507</v>
+        <v>-9.536448015822476</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.740086848063269</v>
       </c>
       <c r="E44">
-        <v>-22.11623589095221</v>
+        <v>-25.24974065140377</v>
       </c>
       <c r="F44">
-        <v>-0.5016287967889848</v>
+        <v>-1.613979597718425</v>
       </c>
       <c r="G44">
-        <v>-8.566027801895913</v>
+        <v>-9.955563081094208</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.782371936913714</v>
       </c>
       <c r="E45">
-        <v>-20.15635309669856</v>
+        <v>-25.03289467354647</v>
       </c>
       <c r="F45">
-        <v>-0.5297609821554587</v>
+        <v>-1.266267410188916</v>
       </c>
       <c r="G45">
-        <v>-8.832112899614835</v>
+        <v>-9.887034788431295</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.819836424884948</v>
       </c>
       <c r="E46">
-        <v>-20.69036886557907</v>
+        <v>-24.15894447480617</v>
       </c>
       <c r="F46">
-        <v>-0.4908459383067436</v>
+        <v>-1.473492628040643</v>
       </c>
       <c r="G46">
-        <v>-9.364107636139096</v>
+        <v>-9.923659353732251</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.846176499269313</v>
       </c>
       <c r="E47">
-        <v>-20.17024645495409</v>
+        <v>-24.14354766318009</v>
       </c>
       <c r="F47">
-        <v>-0.5900329943831508</v>
+        <v>-1.231504972130435</v>
       </c>
       <c r="G47">
-        <v>-8.266539299685745</v>
+        <v>-10.12966798155002</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.859918128345383</v>
       </c>
       <c r="E48">
-        <v>-19.6654755712151</v>
+        <v>-23.4453022559374</v>
       </c>
       <c r="F48">
-        <v>-0.4906479584974745</v>
+        <v>-1.537219760705412</v>
       </c>
       <c r="G48">
-        <v>-8.594822926996493</v>
+        <v>-9.753076873730224</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.861558324370137</v>
       </c>
       <c r="E49">
-        <v>-19.09294965937336</v>
+        <v>-22.42279546737547</v>
       </c>
       <c r="F49">
-        <v>-0.5691448819541585</v>
+        <v>-1.627763631301009</v>
       </c>
       <c r="G49">
-        <v>-9.51522079782467</v>
+        <v>-9.550815783462912</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.849669065586121</v>
       </c>
       <c r="E50">
-        <v>-17.34182045992528</v>
+        <v>-22.71246836422412</v>
       </c>
       <c r="F50">
-        <v>-0.5750784776604113</v>
+        <v>-1.626291622426234</v>
       </c>
       <c r="G50">
-        <v>-8.043190034333275</v>
+        <v>-10.01349100694038</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.829737562724746</v>
       </c>
       <c r="E51">
-        <v>-17.91618040374014</v>
+        <v>-22.1474551907611</v>
       </c>
       <c r="F51">
-        <v>-0.7971695769227783</v>
+        <v>-1.652254313564776</v>
       </c>
       <c r="G51">
-        <v>-8.357390600919963</v>
+        <v>-10.19814992657538</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.811435779885679</v>
       </c>
       <c r="E52">
-        <v>-17.28997396101146</v>
+        <v>-21.79233678755359</v>
       </c>
       <c r="F52">
-        <v>-0.6129414949075711</v>
+        <v>-1.82605987691796</v>
       </c>
       <c r="G52">
-        <v>-7.518783068185022</v>
+        <v>-10.28322432584357</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.799815042531871</v>
       </c>
       <c r="E53">
-        <v>-17.18289366462609</v>
+        <v>-21.76124428501693</v>
       </c>
       <c r="F53">
-        <v>-0.5713292867953408</v>
+        <v>-1.590539285321408</v>
       </c>
       <c r="G53">
-        <v>-8.192075198870917</v>
+        <v>-10.61763246240197</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.805543377059967</v>
       </c>
       <c r="E54">
-        <v>-16.04555836065166</v>
+        <v>-21.08135278292733</v>
       </c>
       <c r="F54">
-        <v>-1.173621971492417</v>
+        <v>-1.547257916892536</v>
       </c>
       <c r="G54">
-        <v>-8.900326690451518</v>
+        <v>-10.84245160997388</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.841539058378336</v>
       </c>
       <c r="E55">
-        <v>-16.67027493543181</v>
+        <v>-21.08619372164152</v>
       </c>
       <c r="F55">
-        <v>-0.4910339777071791</v>
+        <v>-1.82661322634303</v>
       </c>
       <c r="G55">
-        <v>-8.223962373505177</v>
+        <v>-10.74394301690733</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.912384733954246</v>
       </c>
       <c r="E56">
-        <v>-16.77143651628916</v>
+        <v>-20.75615853596251</v>
       </c>
       <c r="F56">
-        <v>-1.663187106546924</v>
+        <v>-1.354290558777794</v>
       </c>
       <c r="G56">
-        <v>-8.510456984473706</v>
+        <v>-10.94765412612084</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.02368097832304</v>
       </c>
       <c r="E57">
-        <v>-15.70849498331274</v>
+        <v>-20.4746595346977</v>
       </c>
       <c r="F57">
-        <v>-0.9423152848739049</v>
+        <v>-1.484144604473242</v>
       </c>
       <c r="G57">
-        <v>-8.674183324663902</v>
+        <v>-10.5363949854138</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.180384048968932</v>
       </c>
       <c r="E58">
-        <v>-15.88402316432406</v>
+        <v>-19.36705819105764</v>
       </c>
       <c r="F58">
-        <v>-0.7293635631666249</v>
+        <v>-1.74629472296759</v>
       </c>
       <c r="G58">
-        <v>-9.513496003598709</v>
+        <v>-11.10717276293062</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.377541909780565</v>
       </c>
       <c r="E59">
-        <v>-17.11920520618222</v>
+        <v>-19.71189242979372</v>
       </c>
       <c r="F59">
-        <v>-1.007633711319452</v>
+        <v>-1.767316202548433</v>
       </c>
       <c r="G59">
-        <v>-8.498754205992382</v>
+        <v>-10.75219289639119</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.607589401283272</v>
       </c>
       <c r="E60">
-        <v>-14.66356319146483</v>
+        <v>-19.50119611963884</v>
       </c>
       <c r="F60">
-        <v>-1.087974580614767</v>
+        <v>-1.781774527196896</v>
       </c>
       <c r="G60">
-        <v>-8.732280088332573</v>
+        <v>-10.86187127010725</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.863359228605619</v>
       </c>
       <c r="E61">
-        <v>-15.3340445245665</v>
+        <v>-19.27288857406814</v>
       </c>
       <c r="F61">
-        <v>-1.395206938271673</v>
+        <v>-1.692074762984751</v>
       </c>
       <c r="G61">
-        <v>-9.051145213584094</v>
+        <v>-10.85331682043377</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.129994090470547</v>
       </c>
       <c r="E62">
-        <v>-15.3584892272599</v>
+        <v>-19.1603424095555</v>
       </c>
       <c r="F62">
-        <v>-1.186157655398981</v>
+        <v>-1.707091407262701</v>
       </c>
       <c r="G62">
-        <v>-8.980216775405209</v>
+        <v>-11.26303655746505</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.389950613426876</v>
       </c>
       <c r="E63">
-        <v>-14.97057561528885</v>
+        <v>-19.07127638277264</v>
       </c>
       <c r="F63">
-        <v>-1.150256212161651</v>
+        <v>-1.982754683198918</v>
       </c>
       <c r="G63">
-        <v>-8.990059027293462</v>
+        <v>-10.7030809533161</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.629743450254704</v>
       </c>
       <c r="E64">
-        <v>-15.24781332251244</v>
+        <v>-18.145167220412</v>
       </c>
       <c r="F64">
-        <v>-0.7825696014484371</v>
+        <v>-1.743382183179347</v>
       </c>
       <c r="G64">
-        <v>-9.432261837156073</v>
+        <v>-11.01266661942105</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.833846421801215</v>
       </c>
       <c r="E65">
-        <v>-14.52288614641655</v>
+        <v>-18.7744032122518</v>
       </c>
       <c r="F65">
-        <v>-1.150695246885135</v>
+        <v>-1.883467394666772</v>
       </c>
       <c r="G65">
-        <v>-9.314873202879054</v>
+        <v>-11.50343182179923</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.986258280961374</v>
       </c>
       <c r="E66">
-        <v>-14.73891699895247</v>
+        <v>-18.92538706414154</v>
       </c>
       <c r="F66">
-        <v>-1.497675985997972</v>
+        <v>-1.983875464294905</v>
       </c>
       <c r="G66">
-        <v>-9.388671884040489</v>
+        <v>-11.40467824836277</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.078327608256531</v>
       </c>
       <c r="E67">
-        <v>-13.88894959855679</v>
+        <v>-19.17222965382564</v>
       </c>
       <c r="F67">
-        <v>-1.25002395378742</v>
+        <v>-2.125770658557447</v>
       </c>
       <c r="G67">
-        <v>-9.03454282770465</v>
+        <v>-11.43471151749504</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.104415774009627</v>
       </c>
       <c r="E68">
-        <v>-14.70552856009391</v>
+        <v>-17.98022208315661</v>
       </c>
       <c r="F68">
-        <v>-1.841332486723375</v>
+        <v>-1.893615723718468</v>
       </c>
       <c r="G68">
-        <v>-9.1079045168549</v>
+        <v>-11.26085490795467</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.059404951649135</v>
       </c>
       <c r="E69">
-        <v>-15.0823655246422</v>
+        <v>-19.37622382244917</v>
       </c>
       <c r="F69">
-        <v>-1.129767372820808</v>
+        <v>-1.944142821819627</v>
       </c>
       <c r="G69">
-        <v>-8.675580374881475</v>
+        <v>-11.02202222111503</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.945106178646387</v>
       </c>
       <c r="E70">
-        <v>-15.24727896257953</v>
+        <v>-18.66012717066824</v>
       </c>
       <c r="F70">
-        <v>-1.323081816877323</v>
+        <v>-1.994859616056027</v>
       </c>
       <c r="G70">
-        <v>-9.047765146588498</v>
+        <v>-10.89740666592578</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.768547897738849</v>
       </c>
       <c r="E71">
-        <v>-14.85566558734422</v>
+        <v>-18.30679751469377</v>
       </c>
       <c r="F71">
-        <v>-1.291326352491004</v>
+        <v>-1.920095316116357</v>
       </c>
       <c r="G71">
-        <v>-8.246328419168494</v>
+        <v>-10.91597551585555</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.535358676310502</v>
       </c>
       <c r="E72">
-        <v>-14.64869168282364</v>
+        <v>-19.78365062891927</v>
       </c>
       <c r="F72">
-        <v>-1.56627060552159</v>
+        <v>-2.291891457514859</v>
       </c>
       <c r="G72">
-        <v>-8.961455913834159</v>
+        <v>-11.00030173183187</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.253831753705199</v>
       </c>
       <c r="E73">
-        <v>-15.28587967502092</v>
+        <v>-18.97858304830964</v>
       </c>
       <c r="F73">
-        <v>-1.717439372858472</v>
+        <v>-2.38554916117758</v>
       </c>
       <c r="G73">
-        <v>-8.505689798897157</v>
+        <v>-10.9798955291278</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.938221299569576</v>
       </c>
       <c r="E74">
-        <v>-15.92853353534545</v>
+        <v>-18.99730828833136</v>
       </c>
       <c r="F74">
-        <v>-2.080569134488886</v>
+        <v>-2.395501167154813</v>
       </c>
       <c r="G74">
-        <v>-8.391972559623191</v>
+        <v>-10.54677354567941</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.598265406321629</v>
       </c>
       <c r="E75">
-        <v>-14.85429345971989</v>
+        <v>-18.83582290521783</v>
       </c>
       <c r="F75">
-        <v>-1.247217445026736</v>
+        <v>-2.305857731926059</v>
       </c>
       <c r="G75">
-        <v>-8.350306033465923</v>
+        <v>-10.69115967882919</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.242937807283174</v>
       </c>
       <c r="E76">
-        <v>-16.17388625708103</v>
+        <v>-20.13151894524049</v>
       </c>
       <c r="F76">
-        <v>-1.424577532905332</v>
+        <v>-2.227763395027136</v>
       </c>
       <c r="G76">
-        <v>-8.55222944808823</v>
+        <v>-10.55060053632281</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.886944601599912</v>
       </c>
       <c r="E77">
-        <v>-16.38502182921465</v>
+        <v>-20.50451576383027</v>
       </c>
       <c r="F77">
-        <v>-1.521657222309018</v>
+        <v>-2.363006799045197</v>
       </c>
       <c r="G77">
-        <v>-8.06183171626491</v>
+        <v>-10.33474965661679</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.539551458532046</v>
       </c>
       <c r="E78">
-        <v>-16.92845229555711</v>
+        <v>-20.17935321618351</v>
       </c>
       <c r="F78">
-        <v>-1.749076380706191</v>
+        <v>-2.808454742961409</v>
       </c>
       <c r="G78">
-        <v>-8.264258333809186</v>
+        <v>-10.23623113191362</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.206631206604654</v>
       </c>
       <c r="E79">
-        <v>-15.57489141466445</v>
+        <v>-20.5853535533412</v>
       </c>
       <c r="F79">
-        <v>-1.980678794487502</v>
+        <v>-2.466369655199117</v>
       </c>
       <c r="G79">
-        <v>-8.12061707340575</v>
+        <v>-9.864122502753998</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.897926179411006</v>
       </c>
       <c r="E80">
-        <v>-16.90693751554667</v>
+        <v>-21.02208864358894</v>
       </c>
       <c r="F80">
-        <v>-1.706553796818284</v>
+        <v>-2.644609469259486</v>
       </c>
       <c r="G80">
-        <v>-8.000884572886928</v>
+        <v>-9.224531725657883</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.618708107917705</v>
       </c>
       <c r="E81">
-        <v>-19.10624525905988</v>
+        <v>-21.53062721770231</v>
       </c>
       <c r="F81">
-        <v>-2.105322409219341</v>
+        <v>-2.760580905651417</v>
       </c>
       <c r="G81">
-        <v>-7.202420715361189</v>
+        <v>-9.624972003542586</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.370691626586617</v>
       </c>
       <c r="E82">
-        <v>-20.51166622428839</v>
+        <v>-22.59201548409409</v>
       </c>
       <c r="F82">
-        <v>-2.291653716070256</v>
+        <v>-2.864046479363284</v>
       </c>
       <c r="G82">
-        <v>-7.12115344346316</v>
+        <v>-9.286117804324945</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.159069886501358</v>
       </c>
       <c r="E83">
-        <v>-19.8261775283253</v>
+        <v>-22.93901886187985</v>
       </c>
       <c r="F83">
-        <v>-2.25894645753812</v>
+        <v>-2.683211390229943</v>
       </c>
       <c r="G83">
-        <v>-7.071303248732814</v>
+        <v>-9.787476752428791</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.9862327887545689</v>
       </c>
       <c r="E84">
-        <v>-19.1245584079469</v>
+        <v>-24.11865011308592</v>
       </c>
       <c r="F84">
-        <v>-2.146914736513904</v>
+        <v>-2.878253808688698</v>
       </c>
       <c r="G84">
-        <v>-6.268876668196568</v>
+        <v>-9.223442556175463</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.8506623441172759</v>
       </c>
       <c r="E85">
-        <v>-23.15429798773049</v>
+        <v>-24.65398819637668</v>
       </c>
       <c r="F85">
-        <v>-2.17032191421481</v>
+        <v>-3.044378749483125</v>
       </c>
       <c r="G85">
-        <v>-5.679430724383794</v>
+        <v>-9.324536685308187</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7543359537889195</v>
       </c>
       <c r="E86">
-        <v>-22.27971380262912</v>
+        <v>-25.31332042647146</v>
       </c>
       <c r="F86">
-        <v>-2.730674357308146</v>
+        <v>-2.836521487303062</v>
       </c>
       <c r="G86">
-        <v>-6.796273056966782</v>
+        <v>-9.194399140159437</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6994745764173875</v>
       </c>
       <c r="E87">
-        <v>-23.92407969887235</v>
+        <v>-26.56708732565709</v>
       </c>
       <c r="F87">
-        <v>-2.638853972544835</v>
+        <v>-3.169486249960531</v>
       </c>
       <c r="G87">
-        <v>-6.638439487836489</v>
+        <v>-8.838104987040914</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6856847488154506</v>
       </c>
       <c r="E88">
-        <v>-23.773322270683</v>
+        <v>-27.40566561392349</v>
       </c>
       <c r="F88">
-        <v>-2.396949981742309</v>
+        <v>-3.199770533839478</v>
       </c>
       <c r="G88">
-        <v>-6.222237702639315</v>
+        <v>-8.742433531501517</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.7180398389965419</v>
       </c>
       <c r="E89">
-        <v>-27.79189916203769</v>
+        <v>-28.97311085067243</v>
       </c>
       <c r="F89">
-        <v>-2.56059644726756</v>
+        <v>-3.135669807476047</v>
       </c>
       <c r="G89">
-        <v>-6.049016717842489</v>
+        <v>-8.479950307329322</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.8029355995616718</v>
       </c>
       <c r="E90">
-        <v>-27.32764453524533</v>
+        <v>-30.14981444343254</v>
       </c>
       <c r="F90">
-        <v>-2.747918481532224</v>
+        <v>-3.108667515246992</v>
       </c>
       <c r="G90">
-        <v>-6.33495846770596</v>
+        <v>-9.275017545131769</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.9414789689591937</v>
       </c>
       <c r="E91">
-        <v>-28.97951411291928</v>
+        <v>-31.37197032980764</v>
       </c>
       <c r="F91">
-        <v>-2.637111087529345</v>
+        <v>-3.519215512115857</v>
       </c>
       <c r="G91">
-        <v>-6.832182544431257</v>
+        <v>-8.351905026961392</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.139340957757419</v>
       </c>
       <c r="E92">
-        <v>-30.04957440703576</v>
+        <v>-32.11851644081614</v>
       </c>
       <c r="F92">
-        <v>-2.81497068095183</v>
+        <v>-3.281130295040238</v>
       </c>
       <c r="G92">
-        <v>-6.622621701249852</v>
+        <v>-9.305279241906247</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.400642661544067</v>
       </c>
       <c r="E93">
-        <v>-31.93436604529423</v>
+        <v>-34.28640563166412</v>
       </c>
       <c r="F93">
-        <v>-2.596564159897115</v>
+        <v>-3.343404471280496</v>
       </c>
       <c r="G93">
-        <v>-5.974082519561087</v>
+        <v>-9.479622501640886</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.719826014084682</v>
       </c>
       <c r="E94">
-        <v>-33.85667835494325</v>
+        <v>-35.68002086515464</v>
       </c>
       <c r="F94">
-        <v>-2.725727347178628</v>
+        <v>-3.411531063221533</v>
       </c>
       <c r="G94">
-        <v>-5.941447161634951</v>
+        <v>-9.256988314124898</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.095078026609426</v>
       </c>
       <c r="E95">
-        <v>-35.64072276771608</v>
+        <v>-37.33306784607058</v>
       </c>
       <c r="F95">
-        <v>-2.161354837079505</v>
+        <v>-3.376781050674094</v>
       </c>
       <c r="G95">
-        <v>-6.791257580474786</v>
+        <v>-9.39243928486418</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.526029282254141</v>
       </c>
       <c r="E96">
-        <v>-38.00708591737224</v>
+        <v>-39.4892328177127</v>
       </c>
       <c r="F96">
-        <v>-2.910348903710165</v>
+        <v>-3.52461646758211</v>
       </c>
       <c r="G96">
-        <v>-6.563611227012342</v>
+        <v>-9.704339022301074</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.994966619352889</v>
       </c>
       <c r="E97">
-        <v>-38.26168578303148</v>
+        <v>-40.63154944309557</v>
       </c>
       <c r="F97">
-        <v>-2.590371285193786</v>
+        <v>-3.530825081266093</v>
       </c>
       <c r="G97">
-        <v>-7.099836840735793</v>
+        <v>-9.914783781141466</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.503040175839434</v>
       </c>
       <c r="E98">
-        <v>-40.71962373407075</v>
+        <v>-42.49118314400443</v>
       </c>
       <c r="F98">
-        <v>-1.96181189852134</v>
+        <v>-3.427315604081878</v>
       </c>
       <c r="G98">
-        <v>-7.033563029585123</v>
+        <v>-10.55538427462706</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.024451686224704</v>
       </c>
       <c r="E99">
-        <v>-43.50682703020773</v>
+        <v>-44.50509742588061</v>
       </c>
       <c r="F99">
-        <v>-3.18042815498411</v>
+        <v>-3.504247741514673</v>
       </c>
       <c r="G99">
-        <v>-7.785818292473714</v>
+        <v>-9.856451968739506</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.568506478493481</v>
       </c>
       <c r="E100">
-        <v>-44.87386238551023</v>
+        <v>-46.68982574732612</v>
       </c>
       <c r="F100">
-        <v>-2.95248629675577</v>
+        <v>-3.559982785477232</v>
       </c>
       <c r="G100">
-        <v>-7.674348913620915</v>
+        <v>-10.65418419570107</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.082022029742165</v>
       </c>
       <c r="E101">
-        <v>-47.68079397866163</v>
+        <v>-48.53580270274635</v>
       </c>
       <c r="F101">
-        <v>-2.504241784487707</v>
+        <v>-3.873953911955912</v>
       </c>
       <c r="G101">
-        <v>-8.247953897028276</v>
+        <v>-10.84867874613325</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.622419647058582</v>
       </c>
       <c r="E102">
-        <v>-48.62707409637094</v>
+        <v>-50.80307944475917</v>
       </c>
       <c r="F102">
-        <v>-2.567002212393409</v>
+        <v>-3.993403663072198</v>
       </c>
       <c r="G102">
-        <v>-7.68813402524644</v>
+        <v>-11.41991668948003</v>
       </c>
     </row>
   </sheetData>
